--- a/sources/hwoarang_step7.xlsx
+++ b/sources/hwoarang_step7.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA183"/>
+  <dimension ref="A1:AB183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -443,10 +443,11 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="110" customWidth="1" min="23" max="23"/>
-    <col width="38" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -649,12 +655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>79055a8d-b137-4a41-bdfa-4b33843fd897</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>685995cd-55b4-492a-9ee9-3104d4b9c39a</t>
         </is>
@@ -721,12 +727,12 @@
           <t>When done from RFF the throw will be the Pick Pocket.</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>d9e3df7f-5eee-4382-8a4a-b0679fe73445</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>fd86acdc-10b2-4ba3-a6cf-9e38b7509a5d</t>
         </is>
@@ -788,12 +794,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>2dfd8c09-7f49-4a4a-acca-9aa87380bcb1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>3382849b-a6a6-41d2-b6b4-8ad677c8f274</t>
         </is>
@@ -855,12 +861,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>a5513795-123e-48d6-afa2-01018392b013</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>62624dfb-90c2-461b-98a0-a755de6d2a3f</t>
         </is>
@@ -922,12 +928,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>c2b3e6c8-ff8a-4883-a0f6-e7f2986bb8bb</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>c4dd723c-f3d8-4af6-a28d-9c597c642097</t>
         </is>
@@ -936,22 +942,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>f+2+3 [~5]</t>
+          <t>f+2+3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>f+2+3 [~5]</t>
+          <t>f+2+3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Human Cannonball [Tag]</t>
+          <t>Human Cannonball</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Human Cannonball [Tag]</t>
+          <t>Human Cannonball</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -996,10 +1002,15 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
           <t>9044c60b-a06f-4304-adbc-335a88214d8b</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>cf2e5304-a38f-4351-b7ea-e805f5e8379c</t>
         </is>
@@ -1016,12 +1027,12 @@
           <t>Can be done from LFF or RFF unless indicated otherwise</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>17408612-fc58-4f13-8e14-136748fa44ab</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1083,12 +1094,12 @@
           <t>In RFF 2+5 throws don't work.</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>b8fbde6d-1dd0-4a06-832a-6464328e437b</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1150,12 +1161,12 @@
           <t>In RFF 2+5 throws don't work.</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>87427b97-ed62-47ff-9c16-7dd832dbaab9</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1217,12 +1228,12 @@
           <t>In RFF 2+5 throws don't work.</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>f5efc0a7-f776-4080-ad07-4baaea997c03</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1354,20 +1365,25 @@
       </c>
       <c r="X15" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y15" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y15" s="1" t="inlineStr">
+      <c r="Z15" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z15" s="1" t="inlineStr">
+      <c r="AA15" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA15" s="1" t="inlineStr">
+      <c r="AB15" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1449,12 +1465,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>fb8930ef-389f-430c-8d21-8c20584f5ba2</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>d1cc9882-fe93-426f-9cc0-e6501dbf92af</t>
         </is>
@@ -1536,12 +1552,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>d814ccec-6128-4196-bb30-98200a5ced79</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>c91adf36-ddfb-4b7a-ab73-41c027bdc028</t>
         </is>
@@ -1623,12 +1639,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>8a8ae3ca-d697-423d-8c1f-8872a6fbd965</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>71805b44-c805-4c43-b0d5-f20e8b83d013</t>
         </is>
@@ -1710,12 +1726,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>37d05aca-87a3-4026-9622-7de3b0f968b2</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>1bff6f51-9208-4e28-9b29-96622110b5e8</t>
         </is>
@@ -1797,12 +1813,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>cc40d009-13c6-416c-87a1-337f76752c32</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>8005f819-14b0-42da-b492-646bd7e8149d</t>
         </is>
@@ -1884,12 +1900,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>7fbec8b5-d858-44e4-8502-45cd64930f22</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>f86ecd41-53cb-4002-9325-1b3976d2b7fa</t>
         </is>
@@ -1971,12 +1987,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>eede42ee-bfce-4b60-9a97-b3df3eb5dbb3</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>6d06ea0c-d4fd-419d-8e92-d64dd04a43da</t>
         </is>
@@ -2058,12 +2074,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>653c5646-c0b6-4030-874b-1ea3fa5005f9</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>3008f0b4-1401-4a6b-ae55-25d501ca067b</t>
         </is>
@@ -2145,12 +2161,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>72e9a383-da37-4116-a72d-d146f841e38e</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>337dbac4-b7d1-488f-ab7d-2df98f9642c2</t>
         </is>
@@ -2232,12 +2248,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>eae8c320-c9ea-4aea-a406-c3e80d86299d</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>7b76db06-4f02-4727-9e9b-927747549a0a</t>
         </is>
@@ -2319,12 +2335,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>6aced227-c677-4318-bf55-c30a1db8b4ac</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>b33374cf-200e-48f6-abe1-8c735dfb8110</t>
         </is>
@@ -2406,12 +2422,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>bacb322b-5c2f-4256-9a65-c4c90c02d185</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>d27f5251-8749-489e-b6e6-b566c7b9a7b6</t>
         </is>
@@ -2493,12 +2509,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>e5e33c13-cd91-44fc-a389-adb00c5e0dfc</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>5a2f28bc-3314-436d-9801-47481aec2173</t>
         </is>
@@ -2580,12 +2596,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>fb224115-0e8e-4cac-97db-af42c1345d29</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>504a18a5-b13f-47d9-ac3c-e1e1d7d1ec3c</t>
         </is>
@@ -2667,12 +2683,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>0c7058ef-d28f-4d09-b6a4-25ed474dd102</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>f1c59582-58f1-4303-b4a0-26a3da956388</t>
         </is>
@@ -2754,12 +2770,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>1cb23ae9-8e53-40a3-8864-e4d52d433b57</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>3ef5b4d6-297c-4eb0-8bc1-ca981fff5fdc</t>
         </is>
@@ -2841,12 +2857,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>ce150b23-f8ea-46bb-8deb-3230bd3514fb</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>2d2e9ba4-e897-4457-b791-b2844d3d5591</t>
         </is>
@@ -2928,12 +2944,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>e92e73e0-920f-469f-8adb-3efafe47a6cc</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>37d282bc-9591-40bd-b862-6100590b902b</t>
         </is>
@@ -3015,12 +3031,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>b63cb3ca-1647-4bd2-a8f8-964109a914d1</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>cca7b804-a817-4969-8860-dda35dcdcd15</t>
         </is>
@@ -3102,12 +3118,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>98cbc5bf-721e-4edd-8f10-4d1d5ab5902f</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>10696b8f-e0b8-4e33-a0c7-a63480118ee9</t>
         </is>
@@ -3189,12 +3205,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>c3acc540-a362-4eab-a78c-6676fbc03ab1</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>4314c676-05bc-4f11-b05c-4dfc41a58468</t>
         </is>
@@ -3276,12 +3292,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>44009ccf-9f23-4f3b-8372-eacf725aa3e3</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>975e45fc-7992-4636-a6b4-0251761f3bfe</t>
         </is>
@@ -3363,12 +3379,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>c8bfad4c-a415-480f-8821-103c4700c120</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>e4b71347-cd55-4b82-b08f-d0e861e1964b</t>
         </is>
@@ -3450,12 +3466,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>bd0d342c-0f41-492a-bbc3-55ce50bc97b9</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>223b379c-73a0-4095-abf6-22fe670b997b</t>
         </is>
@@ -3587,20 +3603,25 @@
       </c>
       <c r="X42" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y42" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y42" s="1" t="inlineStr">
+      <c r="Z42" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z42" s="1" t="inlineStr">
+      <c r="AA42" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA42" s="1" t="inlineStr">
+      <c r="AB42" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3617,12 +3638,12 @@
           <t>Starting from LFF and RFF - Hwoarang will automaticly switch from RFF to LFF</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>61fd2bf5-e35b-4976-9563-a0da67ec87e3</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>8d8803fc-eef3-4c73-8897-0d7aa51298e7</t>
         </is>
@@ -3679,12 +3700,12 @@
           <t>BT</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>c0506ee6-e85b-49be-9a7c-1576629a5141</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>ec7193b5-044c-4141-9592-8b4aea9cebd2</t>
         </is>
@@ -3741,12 +3762,12 @@
           <t>Switch between LFF and RFF.</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>4a180a01-77d6-41d3-9f83-1c20895b8a83</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>d057d40b-1966-4974-8f4c-39e297c452ce</t>
         </is>
@@ -3838,12 +3859,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>dc7eeec0-03e2-492f-891e-040ed83c32f4</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>96383c9b-1ea4-4bf3-8b78-d60e62a5c49e</t>
         </is>
@@ -3940,12 +3961,12 @@
           <t>SH JGc</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>00fc1ea8-521a-4559-adff-705d529dae1d</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>79754830-29d8-41b0-a248-3eaaf24e3f10</t>
         </is>
@@ -4042,12 +4063,12 @@
           <t>SH JGc</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>db644642-b993-4cb4-85ae-73791f4b941a</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>9ffbea5f-1944-498f-b381-3230ac4f39df</t>
         </is>
@@ -4144,12 +4165,12 @@
           <t>SH KNDc</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>b4e0203e-004a-425e-9fc6-ad3954df620a</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>3a2db95e-89ce-4e28-95e1-2951cbb3a891</t>
         </is>
@@ -4246,12 +4267,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>d31219e5-cd70-4c15-8427-5befe6d2caf0</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>fbeb2ca9-b71c-48a3-9db4-ff39ff68433e</t>
         </is>
@@ -4348,12 +4369,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>14fe160d-829d-463f-b420-a3dd09bb11f7</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>98d8896b-78c8-485f-99d9-539f0caea744</t>
         </is>
@@ -4445,12 +4466,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>4aae05ad-7ef5-48e4-93ae-b9dde920ea26</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>c6fa65c0-9004-413f-aa9a-59bd2a3c6779</t>
         </is>
@@ -4547,12 +4568,12 @@
           <t>sh</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>787497cc-d896-4d01-85f4-d7a362a7fd81</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>0e6c9011-4266-4bb4-96d2-5785d3439370</t>
         </is>
@@ -4654,12 +4675,12 @@
           <t>When the 2nd hit is blocked, the 3rd hit will be cancelled.</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>106dcc4e-a739-4d98-bc73-b8ad53d237fd</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>ab6a62b6-f2a4-4394-ab01-e518212a0e26</t>
         </is>
@@ -4668,22 +4689,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>f,N,d,df+4 [~5]</t>
+          <t>f,N,d,df+4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>f,N,d,df+4 [~5]</t>
+          <t>f,N,d,df+4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sky Rocket [Tag]</t>
+          <t>Sky Rocket</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sky Rocket [Tag]</t>
+          <t>Sky Rocket</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4758,10 +4779,15 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
           <t>b8823b87-981f-499d-962f-02f09951ce23</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>8daf2824-ad41-45f7-87f9-0053924eba3e</t>
         </is>
@@ -4770,22 +4796,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>d+4,4 [~5]</t>
+          <t>d+4,4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>d+4,4 [~5]</t>
+          <t>d+4,4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Fire Cracker [Tag]</t>
+          <t>Fire Cracker</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fire Cracker [Tag]</t>
+          <t>Fire Cracker</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4860,10 +4886,15 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
           <t>edfd9db3-5303-4d2b-a76f-5d5390967342</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>45ec78ab-14da-4e89-ac26-7c2992b842ec</t>
         </is>
@@ -4960,12 +4991,12 @@
           <t>OSc</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>ad3b3bed-32af-49a9-ba4a-7c83d85b326d</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>384d0f8d-7103-481e-a464-5fe004f66a9e</t>
         </is>
@@ -5062,12 +5093,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>2dfa3ff9-87ea-42df-8503-d230415288d8</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>a9363e4b-1a0f-4d2e-89a1-9dd1f6c24680</t>
         </is>
@@ -5124,12 +5155,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>f2ac8f19-7f41-4cfe-a393-7c45524882d1</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>01ad4caa-8276-4968-857e-0caca4bb98b9</t>
         </is>
@@ -5226,12 +5257,12 @@
           <t>mM</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>ad5d0e02-7b29-4fe8-b13e-2b65b84dfcc1</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>4b479f76-bb33-43b2-93d0-f1030fcadabc</t>
         </is>
@@ -5288,12 +5319,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>4d45e91f-7204-4df4-b5d3-2aca1f36cbee</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>8fe475a1-b89a-4adb-928a-d69aca88aa31</t>
         </is>
@@ -5425,20 +5456,25 @@
       </c>
       <c r="X64" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y64" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y64" s="1" t="inlineStr">
+      <c r="Z64" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z64" s="1" t="inlineStr">
+      <c r="AA64" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA64" s="1" t="inlineStr">
+      <c r="AB64" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -5455,12 +5491,12 @@
           <t>Moves starting from Left Foot Forward only - LFF</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>4d9f9812-0797-421f-81c0-303629387f4d</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>2a858f70-c204-4593-b770-90e1ba1e198c</t>
         </is>
@@ -5552,12 +5588,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>ad4076f8-893c-4dc0-b6cb-920457f71e47</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>e26af558-5780-4349-b005-8510b7b02f3b</t>
         </is>
@@ -5644,17 +5680,17 @@
           <t>hhm</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>18f4f4dd-41d2-41aa-9013-8672c9407413</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>05f16128-2565-4097-813e-ede00af4faf5</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>ad4076f8-893c-4dc0-b6cb-920457f71e47</t>
         </is>
@@ -5741,17 +5777,17 @@
           <t>hhh</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>590af42f-9c70-4bc0-8444-52bbb1118c9d</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>67156b50-e887-44f2-8f91-b98b4436286f</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>ad4076f8-893c-4dc0-b6cb-920457f71e47</t>
         </is>
@@ -5843,12 +5879,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>d94b8751-a981-4f27-9b51-adfe875dcc48</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>4ed51b0a-be74-4f13-bbe9-443a86b5a70a</t>
         </is>
@@ -5935,17 +5971,17 @@
           <t>hm</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>ebed4a9a-86c2-426b-8eda-fe1d73b0c7d8</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>de4fe130-03bf-47c5-aa6f-7f0ffe223f6f</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>d94b8751-a981-4f27-9b51-adfe875dcc48</t>
         </is>
@@ -6032,17 +6068,17 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>b9567fd5-b0f1-4479-a80f-814c8bfcc826</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>124e84f0-811c-42fa-a461-757a1b854d75</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>d94b8751-a981-4f27-9b51-adfe875dcc48</t>
         </is>
@@ -6134,12 +6170,12 @@
           <t>hhlh</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>bf23d135-aaeb-4efa-8ef1-432eec07a009</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>d9953cfa-4bcc-4a40-b36e-0fa0012b766b</t>
         </is>
@@ -6231,12 +6267,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>1485eb12-e60c-46c1-961b-2ef1dd0bfef1</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>f64658fc-4b1e-48e6-8efa-e1f847409167</t>
         </is>
@@ -6333,12 +6369,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>a55b2932-26c5-4200-be6d-d9c307ca3cf7</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>8823a4d5-d4e2-40cd-aa86-5d8a30fc7149</t>
         </is>
@@ -6430,12 +6466,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>f6557319-3665-49b5-abaf-5a1efc048297</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>17d25627-1064-42b4-86c2-81985eb36c2a</t>
         </is>
@@ -6492,12 +6528,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>c086dc6c-fa4b-4ede-8a91-775dc9eb36f7</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>1d6db9dc-6ce5-4221-8a7a-2d3a5cf25a7a</t>
         </is>
@@ -6594,12 +6630,12 @@
           <t>KNDc</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>92e96eeb-b061-4b68-942f-d11756a04c6e</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>8cb868d7-e296-48af-ab95-7efc6d890280</t>
         </is>
@@ -6696,12 +6732,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>48252121-3d44-4d8e-b88e-1f1a16160b69</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>71d52158-a5fe-469d-a7a3-a2bb5fd18318</t>
         </is>
@@ -6793,12 +6829,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>0ce040a6-0450-4f11-a807-0223952a95bb</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>df035cbf-add8-402e-999f-6d3ac342ff33</t>
         </is>
@@ -6890,12 +6926,12 @@
           <t>mh</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>d5b33742-2c90-48b8-99f4-21a9e7392fb9</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>e45d5a6e-9ec6-4630-8590-6821cda5431c</t>
         </is>
@@ -6947,12 +6983,12 @@
           <t>hml</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>8088c0ca-aec9-4df2-a212-678686b19489</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>26f71767-ba5c-41dd-b3b0-03b5607553e9</t>
         </is>
@@ -7009,12 +7045,12 @@
           <t>hmlh</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>1358e51e-baab-4fc9-b47d-2a0df19da788</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>7c027e0a-3db1-4c0a-b8b5-768b8b01d739</t>
         </is>
@@ -7111,12 +7147,12 @@
           <t>hmlhm</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>2a19e02c-3d03-49d2-9c16-89cc4ec2932d</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>0b24af57-416f-4ce3-9812-b46bc5a1fb20</t>
         </is>
@@ -7173,12 +7209,12 @@
           <t>hmh</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>dd80a6d2-b000-466c-ba7b-6261227faef6</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>e32a9d83-f809-4beb-886d-9ff0f2dfd851</t>
         </is>
@@ -7275,12 +7311,12 @@
           <t>hmhm</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>dec13618-99b7-4f0d-a9be-6daa182015a8</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>d21196fd-d6f7-4a4d-a421-6e099775bba0</t>
         </is>
@@ -7337,12 +7373,12 @@
           <t>hmmh</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>bef0fe5d-b0fe-4e46-bb14-707a6b87f591</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>c4ae966f-765a-4f78-9b5d-30006946f53a</t>
         </is>
@@ -7439,12 +7475,12 @@
           <t>hmmhm</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>e299b6c0-4399-493d-9886-f39401dbeb65</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>5cd5a4f6-39e9-46a8-a708-1c10afe3dc55</t>
         </is>
@@ -7453,22 +7489,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3,3,3&lt;3 [~5]</t>
+          <t>3,3,3&lt;3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3,3,3&lt;3 [~5]</t>
+          <t>3,3,3&lt;3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Machine Gun Kicks [Tag]</t>
+          <t>Machine Gun Kicks</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Machine Gun Kicks [Tag]</t>
+          <t>Machine Gun Kicks</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7543,10 +7579,15 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
           <t>4d18eea5-fe7c-49d3-ada4-0dfdbae3153a</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>52f80fa4-5dd8-45f9-a6e2-e2c72b68e241</t>
         </is>
@@ -7555,22 +7596,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BT 4 [~5]</t>
+          <t>BT 4</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BT 4 [~5]</t>
+          <t>BT 4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Plasma Blade [Tag]</t>
+          <t>Plasma Blade</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Plasma Blade [Tag]</t>
+          <t>Plasma Blade</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7645,10 +7686,15 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
           <t>76d898f4-5db2-4460-b96e-6b4af4f9ab0a</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>013b7e5b-abd7-4d7c-880b-ec85c4ab7b03</t>
         </is>
@@ -7705,12 +7751,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>94ac6ea0-73d0-4dcb-bb73-26ef52608ae1</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>117b3ad3-714f-4adf-8ff8-dbfaf7217eff</t>
         </is>
@@ -7767,12 +7813,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>dbedd772-ce5d-428d-8e39-a81af8bb139a</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>901992a6-1a84-4153-8518-fd4aae256672</t>
         </is>
@@ -7874,12 +7920,12 @@
           <t>OSc</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>3b1a5945-6bb4-4ab6-904c-ccad045e962d</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>10ef7aa7-3b42-4444-a8cb-b28298a158d9</t>
         </is>
@@ -7976,12 +8022,12 @@
           <t>hm</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>0f710a64-407a-434f-ad7a-9acb950a3b96</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>0451d52b-8804-42e4-898b-6e430830c41c</t>
         </is>
@@ -8083,12 +8129,12 @@
           <t>Hwoarang is Back Turned when the move is blocked. On a hit the opponent will be Back Turned.</t>
         </is>
       </c>
-      <c r="X94" t="inlineStr">
+      <c r="Y94" t="inlineStr">
         <is>
           <t>c1959e50-ee51-477b-8e25-15efcf90d2c2</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>6f9f53fe-aee9-4f61-a017-250e991542e7</t>
         </is>
@@ -8195,12 +8241,12 @@
           <t>SHc occurs on first hit.</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
+      <c r="Y95" t="inlineStr">
         <is>
           <t>6ee384d5-e513-49a1-99b9-9d49bb73039e</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>d39927bc-7e56-4948-8ec4-cd3168fc75db</t>
         </is>
@@ -8302,12 +8348,12 @@
           <t>SHc occurs on first hit.</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>10024014-d036-4ee4-9d79-e705d455da7d</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>c33a1ec9-bd32-4314-a897-7355e3c1b579</t>
         </is>
@@ -8409,12 +8455,12 @@
           <t>SHc occurs on first hit.</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>49c08ca9-2e9c-46a1-a364-49df5ee09ad1</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>d8253ea6-f661-4785-8638-f825b8d54e7d</t>
         </is>
@@ -8521,12 +8567,12 @@
           <t>SHc occurs on first hit.</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="Y98" t="inlineStr">
         <is>
           <t>c1a7ef20-2d04-4d79-9249-882299bc5c8d</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>94b2522a-2025-4df8-ad3a-1b45c7b0b75f</t>
         </is>
@@ -8633,12 +8679,12 @@
           <t>SHc occurs on first hit.</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="Y99" t="inlineStr">
         <is>
           <t>de983abe-59d9-4020-849f-fdfceadb2dae</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>ee7e7f95-a8b9-47d0-9c96-e5ee33ef8f0e</t>
         </is>
@@ -8745,12 +8791,12 @@
           <t>SHc occurs on first hit.</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>70cb2e61-cbf6-4782-b9dd-7896aa811268</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>5975e2d6-4f3f-4490-b4cb-5a7c5bc5e204</t>
         </is>
@@ -8852,12 +8898,12 @@
           <t>SHc occurs on first hit.</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
+      <c r="Y101" t="inlineStr">
         <is>
           <t>8d4bde43-5eee-47f6-9f2e-986790804c31</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="Z101" t="inlineStr">
         <is>
           <t>85469bc1-9001-40b9-aeb5-f7538e722bb1</t>
         </is>
@@ -8964,12 +9010,12 @@
           <t>SHc occurs on first hit.</t>
         </is>
       </c>
-      <c r="X102" t="inlineStr">
+      <c r="Y102" t="inlineStr">
         <is>
           <t>947737e9-8125-44f0-aa4b-c421c3e001fc</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>34028510-4595-47f3-b2e1-86178269a614</t>
         </is>
@@ -9101,20 +9147,25 @@
       </c>
       <c r="X105" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y105" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y105" s="1" t="inlineStr">
+      <c r="Z105" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z105" s="1" t="inlineStr">
+      <c r="AA105" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA105" s="1" t="inlineStr">
+      <c r="AB105" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -9131,12 +9182,12 @@
           <t>Moves starting from Right Foot Forward only - RFF</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
+      <c r="Y106" t="inlineStr">
         <is>
           <t>8f877cb5-20a4-4be1-b2e3-456024416adb</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>8a5d81f5-fe70-4dc1-8a46-d44b26b95ac0</t>
         </is>
@@ -9193,12 +9244,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X107" t="inlineStr">
+      <c r="Y107" t="inlineStr">
         <is>
           <t>327897cc-5c04-4f92-bb6b-2225ca10530d</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr">
+      <c r="Z107" t="inlineStr">
         <is>
           <t>46edbbfb-b1bd-4982-96a6-cd1ba6f331a8</t>
         </is>
@@ -9290,12 +9341,12 @@
           <t>hm</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
+      <c r="Y108" t="inlineStr">
         <is>
           <t>ab40dbd8-4c0d-4cce-a95e-6824ccfc0844</t>
         </is>
       </c>
-      <c r="Y108" t="inlineStr">
+      <c r="Z108" t="inlineStr">
         <is>
           <t>c5c078b7-ebd8-45b7-b9dc-b4ffe2eab121</t>
         </is>
@@ -9387,12 +9438,12 @@
           <t>hhm</t>
         </is>
       </c>
-      <c r="X109" t="inlineStr">
+      <c r="Y109" t="inlineStr">
         <is>
           <t>08e5ed4d-97f6-4b7b-bd02-9e142489bf6a</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
+      <c r="Z109" t="inlineStr">
         <is>
           <t>f8879496-5f3b-4b40-91df-febfcaa7267c</t>
         </is>
@@ -9484,12 +9535,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
+      <c r="Y110" t="inlineStr">
         <is>
           <t>8a0f2b92-8826-47de-b652-cf04ed80d288</t>
         </is>
       </c>
-      <c r="Y110" t="inlineStr">
+      <c r="Z110" t="inlineStr">
         <is>
           <t>f0b1f838-6790-48c5-bd78-da0d44322568</t>
         </is>
@@ -9586,12 +9637,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X111" t="inlineStr">
+      <c r="Y111" t="inlineStr">
         <is>
           <t>e6224037-df12-4010-af5d-164213549d04</t>
         </is>
       </c>
-      <c r="Y111" t="inlineStr">
+      <c r="Z111" t="inlineStr">
         <is>
           <t>f01fc145-79a2-42a5-b7c8-5daf9f0c02ba</t>
         </is>
@@ -9688,12 +9739,12 @@
           <t>hhM</t>
         </is>
       </c>
-      <c r="X112" t="inlineStr">
+      <c r="Y112" t="inlineStr">
         <is>
           <t>c2a632f1-ffe4-4498-83a7-748c07b1add8</t>
         </is>
       </c>
-      <c r="Y112" t="inlineStr">
+      <c r="Z112" t="inlineStr">
         <is>
           <t>3644fdee-99de-4fb9-bd6c-97192aade09f</t>
         </is>
@@ -9785,12 +9836,12 @@
           <t>hhh</t>
         </is>
       </c>
-      <c r="X113" t="inlineStr">
+      <c r="Y113" t="inlineStr">
         <is>
           <t>f7d93f9d-c44a-4651-9bd3-6f5df118a0c5</t>
         </is>
       </c>
-      <c r="Y113" t="inlineStr">
+      <c r="Z113" t="inlineStr">
         <is>
           <t>3ce71eaf-4ab2-4567-bc62-9d78c9f5be05</t>
         </is>
@@ -9887,12 +9938,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
+      <c r="Y114" t="inlineStr">
         <is>
           <t>5d1e9ce5-d12f-410c-b696-086699fbaaec</t>
         </is>
       </c>
-      <c r="Y114" t="inlineStr">
+      <c r="Z114" t="inlineStr">
         <is>
           <t>78e3839b-f21d-4f0e-a0d4-4412e8d4ffa4</t>
         </is>
@@ -9949,12 +10000,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
+      <c r="Y115" t="inlineStr">
         <is>
           <t>40c2cb99-3266-497f-aa6f-611e44a4b9ad</t>
         </is>
       </c>
-      <c r="Y115" t="inlineStr">
+      <c r="Z115" t="inlineStr">
         <is>
           <t>b0f94147-e627-4cc6-a782-0eda39c6719e</t>
         </is>
@@ -10051,12 +10102,12 @@
           <t>OSb</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
+      <c r="Y116" t="inlineStr">
         <is>
           <t>243d7dfb-59a0-4a40-9019-42d66c65a260</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
+      <c r="Z116" t="inlineStr">
         <is>
           <t>4c7d5258-a87c-4d05-8098-02632d6694dd</t>
         </is>
@@ -10153,12 +10204,12 @@
           <t>OSb</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
+      <c r="Y117" t="inlineStr">
         <is>
           <t>8eb62d34-2614-4ab7-8c7f-63c2e23a95b1</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
+      <c r="Z117" t="inlineStr">
         <is>
           <t>d3aca059-0a0b-42de-8108-eb900c257f41</t>
         </is>
@@ -10255,12 +10306,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
+      <c r="Y118" t="inlineStr">
         <is>
           <t>79e937ea-9fef-4c2a-b0e3-4662e025f0e5</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>2385acf0-0110-4a0c-9e06-cfd92fa80646</t>
         </is>
@@ -10352,17 +10403,17 @@
           <t>BT</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr">
+      <c r="Y119" t="inlineStr">
         <is>
           <t>86748328-3934-4013-bb61-5f21c8a678d1</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
+      <c r="Z119" t="inlineStr">
         <is>
           <t>b88836cc-2f3a-4284-8731-d7cf7796089d</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
+      <c r="AA119" t="inlineStr">
         <is>
           <t>79e937ea-9fef-4c2a-b0e3-4662e025f0e5</t>
         </is>
@@ -10449,17 +10500,17 @@
           <t>hL</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr">
+      <c r="Y120" t="inlineStr">
         <is>
           <t>56a772b8-d4f6-4c02-a732-0207ce22e832</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="Z120" t="inlineStr">
         <is>
           <t>9d8ea37c-fe34-472f-8dd3-a3e3a6d9518a</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
+      <c r="AA120" t="inlineStr">
         <is>
           <t>79e937ea-9fef-4c2a-b0e3-4662e025f0e5</t>
         </is>
@@ -10468,22 +10519,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BT 3 [~5]</t>
+          <t>BT 3</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BT 3 [~5]</t>
+          <t>BT 3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Plasma Blade [Tag]</t>
+          <t>Plasma Blade</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Plasma Blade [Tag]</t>
+          <t>Plasma Blade</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10558,10 +10609,15 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
           <t>5acf1535-a45a-4272-ba46-014da0dd4555</t>
         </is>
       </c>
-      <c r="Y121" t="inlineStr">
+      <c r="Z121" t="inlineStr">
         <is>
           <t>7939b06c-012e-449a-848e-e37f3d851e86</t>
         </is>
@@ -10663,12 +10719,12 @@
           <t>OSb</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
+      <c r="Y122" t="inlineStr">
         <is>
           <t>ba775b2c-c47f-409d-88a8-f4a8748850cb</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="Z122" t="inlineStr">
         <is>
           <t>43b6d2be-2726-4be4-a774-c81693f5b4e6</t>
         </is>
@@ -10765,12 +10821,12 @@
           <t>OSc</t>
         </is>
       </c>
-      <c r="X123" t="inlineStr">
+      <c r="Y123" t="inlineStr">
         <is>
           <t>2875d86c-435b-4b92-a2f3-792b69d247ed</t>
         </is>
       </c>
-      <c r="Y123" t="inlineStr">
+      <c r="Z123" t="inlineStr">
         <is>
           <t>2344ec19-1bca-4711-88ad-43098056a3ad</t>
         </is>
@@ -10867,12 +10923,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X124" t="inlineStr">
+      <c r="Y124" t="inlineStr">
         <is>
           <t>c145b09c-cdff-480c-accc-320a631bc7f1</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
+      <c r="Z124" t="inlineStr">
         <is>
           <t>46fc77d7-64a4-4f7d-9054-f39b3c6e1bde</t>
         </is>
@@ -10969,12 +11025,12 @@
           <t>hM</t>
         </is>
       </c>
-      <c r="X125" t="inlineStr">
+      <c r="Y125" t="inlineStr">
         <is>
           <t>f9a55337-e215-4ea1-b6e1-2d8c1227e3d7</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
+      <c r="Z125" t="inlineStr">
         <is>
           <t>f56a9bf2-799b-4295-985c-3f475e66fd7c</t>
         </is>
@@ -11076,12 +11132,12 @@
           <t>JGc</t>
         </is>
       </c>
-      <c r="X126" t="inlineStr">
+      <c r="Y126" t="inlineStr">
         <is>
           <t>583efa34-1b9c-441c-a7c9-218ffe6c1a49</t>
         </is>
       </c>
-      <c r="Y126" t="inlineStr">
+      <c r="Z126" t="inlineStr">
         <is>
           <t>634fddf2-3e7a-4af2-8aeb-13e3b9c3b54e</t>
         </is>
@@ -11173,12 +11229,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X127" t="inlineStr">
+      <c r="Y127" t="inlineStr">
         <is>
           <t>f8988a27-a179-422a-a755-c2b6fa53b9a1</t>
         </is>
       </c>
-      <c r="Y127" t="inlineStr">
+      <c r="Z127" t="inlineStr">
         <is>
           <t>21b2e6f2-2fc9-4511-9394-dbf7bf600b0b</t>
         </is>
@@ -11235,12 +11291,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X128" t="inlineStr">
+      <c r="Y128" t="inlineStr">
         <is>
           <t>9e0e3400-ae51-45fe-9249-66d8941b064d</t>
         </is>
       </c>
-      <c r="Y128" t="inlineStr">
+      <c r="Z128" t="inlineStr">
         <is>
           <t>963531ad-d5f7-47e3-9e07-c0853a752cc4</t>
         </is>
@@ -11337,12 +11393,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X129" t="inlineStr">
+      <c r="Y129" t="inlineStr">
         <is>
           <t>95097c1d-3400-4c89-9965-30b5a83aea0c</t>
         </is>
       </c>
-      <c r="Y129" t="inlineStr">
+      <c r="Z129" t="inlineStr">
         <is>
           <t>813f23b2-7271-4793-99a7-1ec1be1d3f26</t>
         </is>
@@ -11444,12 +11500,12 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X130" t="inlineStr">
+      <c r="Y130" t="inlineStr">
         <is>
           <t>6b0ffe3c-e7bc-464b-9491-fe0937ab51d8</t>
         </is>
       </c>
-      <c r="Y130" t="inlineStr">
+      <c r="Z130" t="inlineStr">
         <is>
           <t>393bd201-24b8-4990-a188-0bf58b191204</t>
         </is>
@@ -11541,12 +11597,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X131" t="inlineStr">
+      <c r="Y131" t="inlineStr">
         <is>
           <t>b0e438d5-4df2-4fbc-a0b8-aa43ef454803</t>
         </is>
       </c>
-      <c r="Y131" t="inlineStr">
+      <c r="Z131" t="inlineStr">
         <is>
           <t>24334874-88b0-496b-91b8-0e08c685d5c9</t>
         </is>
@@ -11648,12 +11704,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X132" t="inlineStr">
+      <c r="Y132" t="inlineStr">
         <is>
           <t>7ab07779-6b2c-4391-a695-6f08bb688f67</t>
         </is>
       </c>
-      <c r="Y132" t="inlineStr">
+      <c r="Z132" t="inlineStr">
         <is>
           <t>8c377121-e064-442c-8946-b98fc675e7aa</t>
         </is>
@@ -11725,12 +11781,12 @@
           <t>Recovers Crouching initially and you can go directly in WS moves after the cancel.</t>
         </is>
       </c>
-      <c r="X133" t="inlineStr">
+      <c r="Y133" t="inlineStr">
         <is>
           <t>f6e4626c-ab6b-4bc5-bb59-699c6422a198</t>
         </is>
       </c>
-      <c r="Y133" t="inlineStr">
+      <c r="Z133" t="inlineStr">
         <is>
           <t>5111307e-045c-4b6a-93b6-130268b11f2d</t>
         </is>
@@ -11787,12 +11843,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X134" t="inlineStr">
+      <c r="Y134" t="inlineStr">
         <is>
           <t>797955e6-0b82-449b-ab6b-ba25ffba05ec</t>
         </is>
       </c>
-      <c r="Y134" t="inlineStr">
+      <c r="Z134" t="inlineStr">
         <is>
           <t>2f502b38-343b-4df6-ac00-0ee92b30de1e</t>
         </is>
@@ -11924,20 +11980,25 @@
       </c>
       <c r="X137" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y137" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y137" s="1" t="inlineStr">
+      <c r="Z137" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z137" s="1" t="inlineStr">
+      <c r="AA137" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA137" s="1" t="inlineStr">
+      <c r="AB137" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -11954,12 +12015,12 @@
           <t>Moves starting from Left Flamingo Stance only - LFS</t>
         </is>
       </c>
-      <c r="X138" t="inlineStr">
+      <c r="Y138" t="inlineStr">
         <is>
           <t>50e20029-310c-4260-b667-e5e083c45db5</t>
         </is>
       </c>
-      <c r="Y138" t="inlineStr">
+      <c r="Z138" t="inlineStr">
         <is>
           <t>5e0895c1-65eb-4287-acf4-ebbb932f79d9</t>
         </is>
@@ -12011,12 +12072,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X139" t="inlineStr">
+      <c r="Y139" t="inlineStr">
         <is>
           <t>f9af1731-ba0d-4c47-aec6-0f3d1af88ed6</t>
         </is>
       </c>
-      <c r="Y139" t="inlineStr">
+      <c r="Z139" t="inlineStr">
         <is>
           <t>34ffbf8b-df70-48ec-bd00-13e352df954d</t>
         </is>
@@ -12078,12 +12139,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X140" t="inlineStr">
+      <c r="Y140" t="inlineStr">
         <is>
           <t>afb40a62-682d-4517-a7f5-f09a52a46928</t>
         </is>
       </c>
-      <c r="Y140" t="inlineStr">
+      <c r="Z140" t="inlineStr">
         <is>
           <t>aa972175-158b-4dee-9bc3-70a3ea78bbae</t>
         </is>
@@ -12140,12 +12201,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X141" t="inlineStr">
+      <c r="Y141" t="inlineStr">
         <is>
           <t>02772b84-dc61-452f-8a17-cbf102553bed</t>
         </is>
       </c>
-      <c r="Y141" t="inlineStr">
+      <c r="Z141" t="inlineStr">
         <is>
           <t>0ad6fe90-b327-48e9-8429-72b47be1529c</t>
         </is>
@@ -12202,12 +12263,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X142" t="inlineStr">
+      <c r="Y142" t="inlineStr">
         <is>
           <t>3766c9c4-7a65-4c54-b00c-afd39d592306</t>
         </is>
       </c>
-      <c r="Y142" t="inlineStr">
+      <c r="Z142" t="inlineStr">
         <is>
           <t>435346f1-07a4-4689-b6d4-d4dedd682a7c</t>
         </is>
@@ -12299,12 +12360,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X143" t="inlineStr">
+      <c r="Y143" t="inlineStr">
         <is>
           <t>8f525f7a-ae35-44ff-b6ae-00ed9fca5680</t>
         </is>
       </c>
-      <c r="Y143" t="inlineStr">
+      <c r="Z143" t="inlineStr">
         <is>
           <t>ec7a1f82-ed19-4db2-8a93-25acbad8f505</t>
         </is>
@@ -12401,12 +12462,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X144" t="inlineStr">
+      <c r="Y144" t="inlineStr">
         <is>
           <t>81cae5a7-5f14-474e-9db2-08fa8e7ecd3f</t>
         </is>
       </c>
-      <c r="Y144" t="inlineStr">
+      <c r="Z144" t="inlineStr">
         <is>
           <t>29275e51-f58a-4f82-a7d6-2f45e4038441</t>
         </is>
@@ -12503,12 +12564,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X145" t="inlineStr">
+      <c r="Y145" t="inlineStr">
         <is>
           <t>f2839690-bd09-451e-8a6f-563b3d3beb27</t>
         </is>
       </c>
-      <c r="Y145" t="inlineStr">
+      <c r="Z145" t="inlineStr">
         <is>
           <t>9d5c831b-5e77-48df-8b51-9df35fac8d25</t>
         </is>
@@ -12605,12 +12666,12 @@
           <t>OSb</t>
         </is>
       </c>
-      <c r="X146" t="inlineStr">
+      <c r="Y146" t="inlineStr">
         <is>
           <t>5aeeb779-e13e-4201-83e7-13db3e8a8f1f</t>
         </is>
       </c>
-      <c r="Y146" t="inlineStr">
+      <c r="Z146" t="inlineStr">
         <is>
           <t>744c9b77-17ff-4b28-ac52-75f0ac9fd989</t>
         </is>
@@ -12707,12 +12768,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X147" t="inlineStr">
+      <c r="Y147" t="inlineStr">
         <is>
           <t>81607b52-87be-439d-9aa1-cc985fc337c7</t>
         </is>
       </c>
-      <c r="Y147" t="inlineStr">
+      <c r="Z147" t="inlineStr">
         <is>
           <t>af57af56-837d-4265-904a-11906665ef93</t>
         </is>
@@ -12721,22 +12782,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3,3,3 [~5]</t>
+          <t>3,3,3</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3,3,3 [~5]</t>
+          <t>3,3,3</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Machine Gun Kicks [Tag]</t>
+          <t>Machine Gun Kicks</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Machine Gun Kicks [Tag]</t>
+          <t>Machine Gun Kicks</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -12811,10 +12872,15 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
           <t>76b7648e-29ed-49fa-bbe2-d33c8749326f</t>
         </is>
       </c>
-      <c r="Y148" t="inlineStr">
+      <c r="Z148" t="inlineStr">
         <is>
           <t>37f64901-2a17-4fbb-8e4b-dd149f0f8130</t>
         </is>
@@ -12871,12 +12937,12 @@
           <t>mmh</t>
         </is>
       </c>
-      <c r="X149" t="inlineStr">
+      <c r="Y149" t="inlineStr">
         <is>
           <t>8572b6c9-9019-424a-ae92-76f2a98f899a</t>
         </is>
       </c>
-      <c r="Y149" t="inlineStr">
+      <c r="Z149" t="inlineStr">
         <is>
           <t>8b4dcd90-fac8-4e70-9e32-d9c92d6fd6a0</t>
         </is>
@@ -12973,12 +13039,12 @@
           <t>mmhm</t>
         </is>
       </c>
-      <c r="X150" t="inlineStr">
+      <c r="Y150" t="inlineStr">
         <is>
           <t>50b60c58-b22e-4b5b-bb9a-87e2c9f6be89</t>
         </is>
       </c>
-      <c r="Y150" t="inlineStr">
+      <c r="Z150" t="inlineStr">
         <is>
           <t>db1ae0bb-65a4-472d-93ac-167998b2efab</t>
         </is>
@@ -13070,12 +13136,12 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X151" t="inlineStr">
+      <c r="Y151" t="inlineStr">
         <is>
           <t>c07ac615-1519-4a32-9c75-435d3cd122c5</t>
         </is>
       </c>
-      <c r="Y151" t="inlineStr">
+      <c r="Z151" t="inlineStr">
         <is>
           <t>ee632614-8dc7-489a-86da-0dedbd12b5ad</t>
         </is>
@@ -13172,12 +13238,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X152" t="inlineStr">
+      <c r="Y152" t="inlineStr">
         <is>
           <t>6fab9235-737d-420e-971e-e2dc7db27252</t>
         </is>
       </c>
-      <c r="Y152" t="inlineStr">
+      <c r="Z152" t="inlineStr">
         <is>
           <t>bbab6ca9-0dbd-450d-b904-9b637f133e38</t>
         </is>
@@ -13186,22 +13252,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>b+4 [~5]</t>
+          <t>b+4</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>b+4 [~5]</t>
+          <t>b+4</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Right Heel Lance [Tag]</t>
+          <t>Right Heel Lance</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Right Heel Lance [Tag]</t>
+          <t>Right Heel Lance</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -13281,10 +13347,15 @@
       </c>
       <c r="X153" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
           <t>e80f8866-f165-4925-8989-7e3bb579944e</t>
         </is>
       </c>
-      <c r="Y153" t="inlineStr">
+      <c r="Z153" t="inlineStr">
         <is>
           <t>1fb829b4-5711-43fb-a8f8-edcef45532b4</t>
         </is>
@@ -13386,12 +13457,12 @@
           <t>BS RC</t>
         </is>
       </c>
-      <c r="X154" t="inlineStr">
+      <c r="Y154" t="inlineStr">
         <is>
           <t>ffa21a34-4dd5-403e-b7fe-79d602a77dd1</t>
         </is>
       </c>
-      <c r="Y154" t="inlineStr">
+      <c r="Z154" t="inlineStr">
         <is>
           <t>b24e0a6a-40c8-4c7d-b7f6-2bcbe8b2f12b</t>
         </is>
@@ -13523,20 +13594,25 @@
       </c>
       <c r="X157" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y157" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y157" s="1" t="inlineStr">
+      <c r="Z157" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z157" s="1" t="inlineStr">
+      <c r="AA157" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA157" s="1" t="inlineStr">
+      <c r="AB157" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -13553,12 +13629,12 @@
           <t>Moves starting from Right Flamingo Stance only - RFS</t>
         </is>
       </c>
-      <c r="X158" t="inlineStr">
+      <c r="Y158" t="inlineStr">
         <is>
           <t>8f43919f-096f-4eb9-bf31-703263189c60</t>
         </is>
       </c>
-      <c r="Y158" t="inlineStr">
+      <c r="Z158" t="inlineStr">
         <is>
           <t>e9e2b3d1-9bb1-4c18-9ff5-27d3d4f6a1a3</t>
         </is>
@@ -13615,12 +13691,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X159" t="inlineStr">
+      <c r="Y159" t="inlineStr">
         <is>
           <t>c647c27c-2c7a-47e5-aef7-c2615eacbe7a</t>
         </is>
       </c>
-      <c r="Y159" t="inlineStr">
+      <c r="Z159" t="inlineStr">
         <is>
           <t>93243ff6-d5bc-4b34-91ca-df71e5852138</t>
         </is>
@@ -13682,12 +13758,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X160" t="inlineStr">
+      <c r="Y160" t="inlineStr">
         <is>
           <t>9d279803-489f-4c70-ac4c-2214c707bc07</t>
         </is>
       </c>
-      <c r="Y160" t="inlineStr">
+      <c r="Z160" t="inlineStr">
         <is>
           <t>87a31dc7-98b9-47ee-880d-b076529bf3ee</t>
         </is>
@@ -13744,12 +13820,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X161" t="inlineStr">
+      <c r="Y161" t="inlineStr">
         <is>
           <t>e24e2ab5-ae0d-497c-99ea-cccf752b8538</t>
         </is>
       </c>
-      <c r="Y161" t="inlineStr">
+      <c r="Z161" t="inlineStr">
         <is>
           <t>cf391bdf-d5cb-4021-a754-e910400db934</t>
         </is>
@@ -13806,12 +13882,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X162" t="inlineStr">
+      <c r="Y162" t="inlineStr">
         <is>
           <t>e8d4894f-8307-4155-9f58-782bb9801dbf</t>
         </is>
       </c>
-      <c r="Y162" t="inlineStr">
+      <c r="Z162" t="inlineStr">
         <is>
           <t>01f83c3c-ed3d-488f-8385-fb97ad36eade</t>
         </is>
@@ -13903,12 +13979,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X163" t="inlineStr">
+      <c r="Y163" t="inlineStr">
         <is>
           <t>99f78834-9ce4-4a0d-b458-f4f94ede931b</t>
         </is>
       </c>
-      <c r="Y163" t="inlineStr">
+      <c r="Z163" t="inlineStr">
         <is>
           <t>fceb10f0-80d5-4328-9c77-2b960edd4138</t>
         </is>
@@ -14005,12 +14081,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X164" t="inlineStr">
+      <c r="Y164" t="inlineStr">
         <is>
           <t>3b146bad-7a95-4cc1-baf5-01c6c41e5ee8</t>
         </is>
       </c>
-      <c r="Y164" t="inlineStr">
+      <c r="Z164" t="inlineStr">
         <is>
           <t>3daafeff-feba-414e-89dd-3f1a1f9f4e90</t>
         </is>
@@ -14107,12 +14183,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X165" t="inlineStr">
+      <c r="Y165" t="inlineStr">
         <is>
           <t>e08662b0-454a-42a7-a077-0eb3c300f767</t>
         </is>
       </c>
-      <c r="Y165" t="inlineStr">
+      <c r="Z165" t="inlineStr">
         <is>
           <t>cd986041-0b40-4314-8093-d36d21e24e08</t>
         </is>
@@ -14121,22 +14197,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>b+3 [~5]</t>
+          <t>b+3</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>b+3 [~5]</t>
+          <t>b+3</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Left Heel Lance [Tag]</t>
+          <t>Left Heel Lance</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Left Heel Lance [Tag]</t>
+          <t>Left Heel Lance</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -14211,10 +14287,15 @@
       </c>
       <c r="X166" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
           <t>6375ed02-a2d0-4da6-99fb-fbc151de4fa2</t>
         </is>
       </c>
-      <c r="Y166" t="inlineStr">
+      <c r="Z166" t="inlineStr">
         <is>
           <t>ca917dbf-4103-44b6-8c6d-587df57560b6</t>
         </is>
@@ -14316,12 +14397,12 @@
           <t>BS RC</t>
         </is>
       </c>
-      <c r="X167" t="inlineStr">
+      <c r="Y167" t="inlineStr">
         <is>
           <t>dcdc440c-989b-414d-92ec-b1de0c75b407</t>
         </is>
       </c>
-      <c r="Y167" t="inlineStr">
+      <c r="Z167" t="inlineStr">
         <is>
           <t>592ec583-a70b-4078-a610-c1d572dbafbc</t>
         </is>
@@ -14423,12 +14504,12 @@
           <t>FSc</t>
         </is>
       </c>
-      <c r="X168" t="inlineStr">
+      <c r="Y168" t="inlineStr">
         <is>
           <t>bb2b2faa-e6d6-4965-a015-3a6f0bfbc4e5</t>
         </is>
       </c>
-      <c r="Y168" t="inlineStr">
+      <c r="Z168" t="inlineStr">
         <is>
           <t>bd0ef25f-f552-42c0-92e7-92aaf94c83bd</t>
         </is>
@@ -14525,12 +14606,12 @@
           <t>GB JG</t>
         </is>
       </c>
-      <c r="X169" t="inlineStr">
+      <c r="Y169" t="inlineStr">
         <is>
           <t>a906ae75-f5ec-47a4-83aa-c9b04bcd66da</t>
         </is>
       </c>
-      <c r="Y169" t="inlineStr">
+      <c r="Z169" t="inlineStr">
         <is>
           <t>99ac4102-7f1a-4b5a-b6e8-35d909eca5f3</t>
         </is>
@@ -14622,12 +14703,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X170" t="inlineStr">
+      <c r="Y170" t="inlineStr">
         <is>
           <t>9cc41b32-8e08-407a-975b-28111f217d3c</t>
         </is>
       </c>
-      <c r="Y170" t="inlineStr">
+      <c r="Z170" t="inlineStr">
         <is>
           <t>8eceeff8-593b-4a1e-8af1-41a51a814017</t>
         </is>
@@ -14724,12 +14805,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X171" t="inlineStr">
+      <c r="Y171" t="inlineStr">
         <is>
           <t>3e290212-cd3e-482e-a19a-8099d7f9f014</t>
         </is>
       </c>
-      <c r="Y171" t="inlineStr">
+      <c r="Z171" t="inlineStr">
         <is>
           <t>83c661cb-561c-49f4-827e-343f5ffd66d2</t>
         </is>
@@ -14861,20 +14942,25 @@
       </c>
       <c r="X174" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y174" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y174" s="1" t="inlineStr">
+      <c r="Z174" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z174" s="1" t="inlineStr">
+      <c r="AA174" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA174" s="1" t="inlineStr">
+      <c r="AB174" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -14956,12 +15042,12 @@
           <t>[!]</t>
         </is>
       </c>
-      <c r="X175" t="inlineStr">
+      <c r="Y175" t="inlineStr">
         <is>
           <t>5c727428-ed3b-4620-b61e-73da1e48b4d9</t>
         </is>
       </c>
-      <c r="Y175" t="inlineStr">
+      <c r="Z175" t="inlineStr">
         <is>
           <t>f8336903-2056-4691-90e1-71f5ce4dbab5</t>
         </is>
@@ -15033,17 +15119,17 @@
           <t>[!]-</t>
         </is>
       </c>
-      <c r="X176" t="inlineStr">
+      <c r="Y176" t="inlineStr">
         <is>
           <t>c3611f8c-ffb2-440a-96b2-89b06edfd130</t>
         </is>
       </c>
-      <c r="Y176" t="inlineStr">
+      <c r="Z176" t="inlineStr">
         <is>
           <t>799e97dc-516a-4b71-9d33-001dc9627600</t>
         </is>
       </c>
-      <c r="Z176" t="inlineStr">
+      <c r="AA176" t="inlineStr">
         <is>
           <t>5c727428-ed3b-4620-b61e-73da1e48b4d9</t>
         </is>
@@ -15125,12 +15211,12 @@
           <t>!</t>
         </is>
       </c>
-      <c r="X177" t="inlineStr">
+      <c r="Y177" t="inlineStr">
         <is>
           <t>f2e6a842-fe8e-4ca4-a036-3b6faa974c5a</t>
         </is>
       </c>
-      <c r="Y177" t="inlineStr">
+      <c r="Z177" t="inlineStr">
         <is>
           <t>f6fcbabe-c7e0-4564-94b5-34c2dd32bfce</t>
         </is>
@@ -15197,17 +15283,17 @@
           <t>!-</t>
         </is>
       </c>
-      <c r="X178" t="inlineStr">
+      <c r="Y178" t="inlineStr">
         <is>
           <t>39b67dd6-af60-4831-9c3b-16b514f796be</t>
         </is>
       </c>
-      <c r="Y178" t="inlineStr">
+      <c r="Z178" t="inlineStr">
         <is>
           <t>7405b99c-9513-4b6e-b896-91c4a9908a60</t>
         </is>
       </c>
-      <c r="Z178" t="inlineStr">
+      <c r="AA178" t="inlineStr">
         <is>
           <t>f2e6a842-fe8e-4ca4-a036-3b6faa974c5a</t>
         </is>
@@ -15339,20 +15425,25 @@
       </c>
       <c r="X181" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y181" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y181" s="1" t="inlineStr">
+      <c r="Z181" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z181" s="1" t="inlineStr">
+      <c r="AA181" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA181" s="1" t="inlineStr">
+      <c r="AB181" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -15394,12 +15485,12 @@
           <t>mhhLmmlhmh</t>
         </is>
       </c>
-      <c r="Y182" t="inlineStr">
+      <c r="Z182" t="inlineStr">
         <is>
           <t>43ddfb49-7ac4-4b7a-99bd-30c709526e89</t>
         </is>
       </c>
-      <c r="AA182" t="inlineStr">
+      <c r="AB182" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -15441,12 +15532,12 @@
           <t>mhhLmmlhmh</t>
         </is>
       </c>
-      <c r="Y183" t="inlineStr">
+      <c r="Z183" t="inlineStr">
         <is>
           <t>b3e0a845-335b-4f9e-b80f-b2fcded6fdb7</t>
         </is>
       </c>
-      <c r="AA183" t="inlineStr">
+      <c r="AB183" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/hwoarang_step7.xlsx
+++ b/sources/hwoarang_step7.xlsx
@@ -425,7 +425,7 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -6997,27 +6997,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3,3,d+3,4 [F]</t>
+          <t>3,3,d+3,4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3,3,d+3,4 [F]</t>
+          <t>3,3,d+3,4</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Menace to Society [LFF]</t>
+          <t>Menace to Society</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Menace to Society [LFF]</t>
+          <t>Menace to Society</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>RFS; (~F)LFF</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7161,27 +7161,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3,3,4 [F]</t>
+          <t>3,3,4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3,3,4 [F]</t>
+          <t>3,3,4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Disorderly Conduct [LFF]</t>
+          <t>Disorderly Conduct</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Disorderly Conduct [LFF]</t>
+          <t>Disorderly Conduct</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>RFS; (~F)LFF</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7325,27 +7325,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3,3,3&lt;4 [F]</t>
+          <t>3,3,3&lt;4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3,3,3&lt;4 [F]</t>
+          <t>3,3,3&lt;4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Party Hearthy [LFF]</t>
+          <t>Party Hearthy</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Party Hearthy [LFF]</t>
+          <t>Party Hearthy</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>RFS; (~F)LFF</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -15034,12 +15034,12 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="Y176" t="inlineStr">

--- a/sources/hwoarang_step7.xlsx
+++ b/sources/hwoarang_step7.xlsx
@@ -1027,6 +1027,11 @@
           <t>Can be done from LFF or RFF unless indicated otherwise</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>17408612-fc58-4f13-8e14-136748fa44ab</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>17408612-fc58-4f13-8e14-136748fa44ab</t>
@@ -1094,6 +1099,11 @@
           <t>In RFF 2+5 throws don't work.</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>b8fbde6d-1dd0-4a06-832a-6464328e437b</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>b8fbde6d-1dd0-4a06-832a-6464328e437b</t>
@@ -1161,6 +1171,11 @@
           <t>In RFF 2+5 throws don't work.</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>87427b97-ed62-47ff-9c16-7dd832dbaab9</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>87427b97-ed62-47ff-9c16-7dd832dbaab9</t>
@@ -1226,6 +1241,11 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>In RFF 2+5 throws don't work.</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>f5efc0a7-f776-4080-ad07-4baaea997c03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -15485,6 +15505,11 @@
           <t>mhhLmmlhmh</t>
         </is>
       </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>43ddfb49-7ac4-4b7a-99bd-30c709526e89</t>
+        </is>
+      </c>
       <c r="Z182" t="inlineStr">
         <is>
           <t>43ddfb49-7ac4-4b7a-99bd-30c709526e89</t>
@@ -15530,6 +15555,11 @@
       <c r="S183" t="inlineStr">
         <is>
           <t>mhhLmmlhmh</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>b3e0a845-335b-4f9e-b80f-b2fcded6fdb7</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
